--- a/july 2026/LMT_JULY_26/July Orders/Zubaida Traders.xlsx
+++ b/july 2026/LMT_JULY_26/July Orders/Zubaida Traders.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6E538B-5657-447A-82AB-AF6D97F5C55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4052A8-69B7-41F1-8511-6F4997C20778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3462,140 +3462,152 @@
     <xf numFmtId="43" fontId="29" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3606,34 +3618,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="43" fontId="29" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9671,28 +9671,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22 16383:16384" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="358" t="s">
+      <c r="A2" s="341" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="358"/>
-      <c r="C2" s="358"/>
+      <c r="B2" s="341"/>
+      <c r="C2" s="341"/>
     </row>
     <row r="3" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="326" t="s">
+      <c r="A3" s="342" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="326"/>
-      <c r="C3" s="326"/>
+      <c r="B3" s="342"/>
+      <c r="C3" s="342"/>
       <c r="F3" s="85"/>
       <c r="G3" s="1"/>
-      <c r="K3" s="325" t="s">
+      <c r="K3" s="326" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="325"/>
-      <c r="M3" s="325"/>
-      <c r="N3" s="326"/>
-      <c r="O3" s="326"/>
-      <c r="P3" s="326"/>
+      <c r="L3" s="326"/>
+      <c r="M3" s="326"/>
+      <c r="N3" s="342"/>
+      <c r="O3" s="342"/>
+      <c r="P3" s="342"/>
       <c r="R3" s="85"/>
       <c r="S3" s="266"/>
       <c r="XFC3" t="s">
@@ -9703,23 +9703,23 @@
       </c>
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="326" t="s">
+      <c r="A4" s="342" t="s">
         <v>495</v>
       </c>
-      <c r="B4" s="326"/>
-      <c r="C4" s="326"/>
+      <c r="B4" s="342"/>
+      <c r="C4" s="342"/>
       <c r="F4" s="85"/>
       <c r="G4" s="1"/>
-      <c r="K4" s="325" t="s">
+      <c r="K4" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="325"/>
-      <c r="M4" s="325"/>
-      <c r="N4" s="327">
+      <c r="L4" s="326"/>
+      <c r="M4" s="326"/>
+      <c r="N4" s="368">
         <v>46222</v>
       </c>
-      <c r="O4" s="327"/>
-      <c r="P4" s="327"/>
+      <c r="O4" s="368"/>
+      <c r="P4" s="368"/>
       <c r="R4" s="85"/>
       <c r="S4" s="266"/>
       <c r="XFC4" s="87" t="s">
@@ -9730,44 +9730,44 @@
       </c>
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="359" t="s">
+      <c r="A5" s="343" t="s">
         <v>496</v>
       </c>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
+      <c r="B5" s="343"/>
+      <c r="C5" s="343"/>
       <c r="F5" s="85"/>
       <c r="G5" s="1"/>
-      <c r="K5" s="325" t="s">
+      <c r="K5" s="326" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="325"/>
-      <c r="M5" s="325"/>
-      <c r="N5" s="327">
+      <c r="L5" s="326"/>
+      <c r="M5" s="326"/>
+      <c r="N5" s="368">
         <v>46221</v>
       </c>
-      <c r="O5" s="326"/>
-      <c r="P5" s="326"/>
+      <c r="O5" s="342"/>
+      <c r="P5" s="342"/>
       <c r="R5" s="85"/>
       <c r="S5" s="266"/>
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="359" t="s">
+      <c r="A6" s="343" t="s">
         <v>497</v>
       </c>
-      <c r="B6" s="359"/>
-      <c r="C6" s="359"/>
+      <c r="B6" s="343"/>
+      <c r="C6" s="343"/>
       <c r="F6" s="85"/>
       <c r="G6" s="86"/>
-      <c r="K6" s="325" t="s">
+      <c r="K6" s="326" t="s">
         <v>69</v>
       </c>
-      <c r="L6" s="325"/>
-      <c r="M6" s="325"/>
-      <c r="N6" s="324" t="s">
+      <c r="L6" s="326"/>
+      <c r="M6" s="326"/>
+      <c r="N6" s="348" t="s">
         <v>499</v>
       </c>
-      <c r="O6" s="324"/>
-      <c r="P6" s="324"/>
+      <c r="O6" s="348"/>
+      <c r="P6" s="348"/>
       <c r="R6" s="85"/>
       <c r="S6" s="267"/>
       <c r="XFC6" t="s">
@@ -9778,23 +9778,23 @@
       </c>
     </row>
     <row r="7" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="325" t="s">
+      <c r="A7" s="326" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="325"/>
-      <c r="C7" s="325"/>
+      <c r="B7" s="326"/>
+      <c r="C7" s="326"/>
       <c r="F7" s="85"/>
       <c r="G7" s="86"/>
-      <c r="K7" s="325" t="s">
+      <c r="K7" s="326" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="325"/>
-      <c r="M7" s="325"/>
-      <c r="N7" s="324" t="s">
+      <c r="L7" s="326"/>
+      <c r="M7" s="326"/>
+      <c r="N7" s="348" t="s">
         <v>500</v>
       </c>
-      <c r="O7" s="324"/>
-      <c r="P7" s="324"/>
+      <c r="O7" s="348"/>
+      <c r="P7" s="348"/>
       <c r="R7" s="85"/>
       <c r="S7" s="267"/>
       <c r="T7" s="268"/>
@@ -9807,44 +9807,44 @@
       </c>
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="366" t="s">
+      <c r="A8" s="327" t="s">
         <v>498</v>
       </c>
-      <c r="B8" s="366"/>
-      <c r="C8" s="366"/>
+      <c r="B8" s="327"/>
+      <c r="C8" s="327"/>
       <c r="F8" s="85"/>
       <c r="G8" s="86"/>
-      <c r="K8" s="325" t="s">
+      <c r="K8" s="326" t="s">
         <v>67</v>
       </c>
-      <c r="L8" s="325"/>
-      <c r="M8" s="325"/>
-      <c r="N8" s="324" t="s">
+      <c r="L8" s="326"/>
+      <c r="M8" s="326"/>
+      <c r="N8" s="348" t="s">
         <v>501</v>
       </c>
-      <c r="O8" s="324"/>
-      <c r="P8" s="324"/>
+      <c r="O8" s="348"/>
+      <c r="P8" s="348"/>
       <c r="R8" s="85"/>
       <c r="S8" s="267"/>
     </row>
     <row r="9" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A9" s="366" t="s">
+      <c r="A9" s="327" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="366"/>
-      <c r="C9" s="366"/>
+      <c r="B9" s="327"/>
+      <c r="C9" s="327"/>
       <c r="F9" s="85"/>
       <c r="G9" s="86"/>
-      <c r="K9" s="325" t="s">
+      <c r="K9" s="326" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="325"/>
-      <c r="M9" s="325"/>
-      <c r="N9" s="324" t="s">
+      <c r="L9" s="326"/>
+      <c r="M9" s="326"/>
+      <c r="N9" s="348" t="s">
         <v>108</v>
       </c>
-      <c r="O9" s="324"/>
-      <c r="P9" s="324"/>
+      <c r="O9" s="348"/>
+      <c r="P9" s="348"/>
       <c r="R9" s="85"/>
       <c r="S9" s="267"/>
       <c r="XFD9" t="s">
@@ -9852,23 +9852,23 @@
       </c>
     </row>
     <row r="10" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
-      <c r="A10" s="366" t="s">
+      <c r="A10" s="327" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="366"/>
-      <c r="C10" s="366"/>
+      <c r="B10" s="327"/>
+      <c r="C10" s="327"/>
       <c r="F10" s="85"/>
       <c r="G10" s="1"/>
-      <c r="K10" s="325" t="s">
+      <c r="K10" s="326" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="325"/>
-      <c r="M10" s="325"/>
-      <c r="N10" s="326" t="s">
+      <c r="L10" s="326"/>
+      <c r="M10" s="326"/>
+      <c r="N10" s="342" t="s">
         <v>47</v>
       </c>
-      <c r="O10" s="326"/>
-      <c r="P10" s="326"/>
+      <c r="O10" s="342"/>
+      <c r="P10" s="342"/>
       <c r="R10" s="85"/>
       <c r="S10" s="266"/>
       <c r="XFD10" t="s">
@@ -9888,16 +9888,16 @@
       </c>
       <c r="F11" s="85"/>
       <c r="G11" s="86"/>
-      <c r="K11" s="325" t="s">
+      <c r="K11" s="326" t="s">
         <v>48</v>
       </c>
-      <c r="L11" s="325"/>
-      <c r="M11" s="325"/>
-      <c r="N11" s="324" t="s">
+      <c r="L11" s="326"/>
+      <c r="M11" s="326"/>
+      <c r="N11" s="348" t="s">
         <v>49</v>
       </c>
-      <c r="O11" s="324"/>
-      <c r="P11" s="324"/>
+      <c r="O11" s="348"/>
+      <c r="P11" s="348"/>
       <c r="Q11" s="282"/>
       <c r="R11" s="85"/>
       <c r="S11" s="267"/>
@@ -9917,14 +9917,14 @@
       </c>
       <c r="F12" s="85"/>
       <c r="G12" s="1"/>
-      <c r="K12" s="325" t="s">
+      <c r="K12" s="326" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="325"/>
-      <c r="M12" s="325"/>
-      <c r="N12" s="326"/>
-      <c r="O12" s="326"/>
-      <c r="P12" s="326"/>
+      <c r="L12" s="326"/>
+      <c r="M12" s="326"/>
+      <c r="N12" s="342"/>
+      <c r="O12" s="342"/>
+      <c r="P12" s="342"/>
       <c r="R12" s="85"/>
       <c r="S12" s="266"/>
       <c r="XFD12" t="s">
@@ -9940,36 +9940,36 @@
       </c>
     </row>
     <row r="14" spans="1:22 16383:16384" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="347" t="s">
+      <c r="A14" s="360" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="348"/>
-      <c r="C14" s="364" t="s">
+      <c r="B14" s="337"/>
+      <c r="C14" s="324" t="s">
         <v>90</v>
       </c>
       <c r="D14" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="367" t="s">
+      <c r="E14" s="328" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="368"/>
-      <c r="G14" s="345" t="s">
+      <c r="F14" s="329"/>
+      <c r="G14" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="346"/>
-      <c r="I14" s="351" t="s">
+      <c r="H14" s="336"/>
+      <c r="I14" s="362" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="362" t="s">
+      <c r="J14" s="334" t="s">
         <v>55</v>
       </c>
-      <c r="K14" s="345"/>
-      <c r="L14" s="346"/>
-      <c r="M14" s="348" t="s">
+      <c r="K14" s="335"/>
+      <c r="L14" s="336"/>
+      <c r="M14" s="337" t="s">
         <v>84</v>
       </c>
-      <c r="N14" s="363" t="s">
+      <c r="N14" s="339" t="s">
         <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
@@ -9986,9 +9986,9 @@
       </c>
     </row>
     <row r="15" spans="1:22 16383:16384" ht="30.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="349"/>
-      <c r="B15" s="350"/>
-      <c r="C15" s="365"/>
+      <c r="A15" s="361"/>
+      <c r="B15" s="338"/>
+      <c r="C15" s="325"/>
       <c r="D15" s="111" t="s">
         <v>57</v>
       </c>
@@ -10004,7 +10004,7 @@
       <c r="H15" s="146" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="352"/>
+      <c r="I15" s="340"/>
       <c r="J15" s="143" t="s">
         <v>59</v>
       </c>
@@ -10014,8 +10014,8 @@
       <c r="L15" s="145" t="s">
         <v>492</v>
       </c>
-      <c r="M15" s="350"/>
-      <c r="N15" s="352"/>
+      <c r="M15" s="338"/>
+      <c r="N15" s="340"/>
       <c r="O15" s="228">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
         <v>5.0000000000000001E-3</v>
@@ -10726,17 +10726,17 @@
       </c>
     </row>
     <row r="25" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="357">
+      <c r="A25" s="367">
         <f>COUNT(A16:A24)</f>
         <v>0</v>
       </c>
-      <c r="B25" s="355"/>
-      <c r="C25" s="355" t="s">
+      <c r="B25" s="365"/>
+      <c r="C25" s="365" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="355"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="356"/>
+      <c r="D25" s="365"/>
+      <c r="E25" s="365"/>
+      <c r="F25" s="366"/>
       <c r="G25" s="117">
         <f t="shared" ref="G25" si="8">SUM(G16:G24)</f>
         <v>0</v>
@@ -10786,7 +10786,10 @@
       <c r="E26" s="122"/>
       <c r="F26" s="122"/>
       <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
+      <c r="H26" s="123">
+        <f>H25/40</f>
+        <v>304.47500000000002</v>
+      </c>
       <c r="I26" s="124"/>
       <c r="K26" s="125"/>
       <c r="L26" s="125"/>
@@ -10806,104 +10809,104 @@
       <c r="H27" s="94"/>
     </row>
     <row r="28" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
-      <c r="B28" s="332" t="s">
+      <c r="B28" s="349" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="333"/>
-      <c r="D28" s="333"/>
-      <c r="E28" s="333"/>
-      <c r="F28" s="333"/>
-      <c r="G28" s="333"/>
-      <c r="H28" s="333"/>
-      <c r="I28" s="333"/>
-      <c r="J28" s="333"/>
-      <c r="K28" s="333"/>
-      <c r="L28" s="334"/>
-      <c r="N28" s="353" t="s">
+      <c r="C28" s="350"/>
+      <c r="D28" s="350"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
+      <c r="G28" s="350"/>
+      <c r="H28" s="350"/>
+      <c r="I28" s="350"/>
+      <c r="J28" s="350"/>
+      <c r="K28" s="350"/>
+      <c r="L28" s="351"/>
+      <c r="N28" s="363" t="s">
         <v>60</v>
       </c>
-      <c r="O28" s="354"/>
+      <c r="O28" s="364"/>
       <c r="P28" s="139">
         <f>I25</f>
         <v>832543.9</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="335"/>
-      <c r="C29" s="336"/>
-      <c r="D29" s="336"/>
-      <c r="E29" s="336"/>
-      <c r="F29" s="336"/>
-      <c r="G29" s="336"/>
-      <c r="H29" s="336"/>
-      <c r="I29" s="336"/>
-      <c r="J29" s="336"/>
-      <c r="K29" s="336"/>
-      <c r="L29" s="337"/>
-      <c r="N29" s="341" t="s">
+      <c r="B29" s="352"/>
+      <c r="C29" s="353"/>
+      <c r="D29" s="353"/>
+      <c r="E29" s="353"/>
+      <c r="F29" s="353"/>
+      <c r="G29" s="353"/>
+      <c r="H29" s="353"/>
+      <c r="I29" s="353"/>
+      <c r="J29" s="353"/>
+      <c r="K29" s="353"/>
+      <c r="L29" s="354"/>
+      <c r="N29" s="332" t="s">
         <v>85</v>
       </c>
-      <c r="O29" s="342"/>
+      <c r="O29" s="333"/>
       <c r="P29" s="140">
         <f>+J25</f>
         <v>149857.902</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="335"/>
-      <c r="C30" s="336"/>
-      <c r="D30" s="336"/>
-      <c r="E30" s="336"/>
-      <c r="F30" s="336"/>
-      <c r="G30" s="336"/>
-      <c r="H30" s="336"/>
-      <c r="I30" s="336"/>
-      <c r="J30" s="336"/>
-      <c r="K30" s="336"/>
-      <c r="L30" s="337"/>
-      <c r="N30" s="341" t="s">
+      <c r="B30" s="352"/>
+      <c r="C30" s="353"/>
+      <c r="D30" s="353"/>
+      <c r="E30" s="353"/>
+      <c r="F30" s="353"/>
+      <c r="G30" s="353"/>
+      <c r="H30" s="353"/>
+      <c r="I30" s="353"/>
+      <c r="J30" s="353"/>
+      <c r="K30" s="353"/>
+      <c r="L30" s="354"/>
+      <c r="N30" s="332" t="s">
         <v>86</v>
       </c>
-      <c r="O30" s="342"/>
+      <c r="O30" s="333"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
         <v>29139.036500000002</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="335"/>
-      <c r="C31" s="336"/>
-      <c r="D31" s="336"/>
-      <c r="E31" s="336"/>
-      <c r="F31" s="336"/>
-      <c r="G31" s="336"/>
-      <c r="H31" s="336"/>
-      <c r="I31" s="336"/>
-      <c r="J31" s="336"/>
-      <c r="K31" s="336"/>
-      <c r="L31" s="337"/>
+      <c r="B31" s="352"/>
+      <c r="C31" s="353"/>
+      <c r="D31" s="353"/>
+      <c r="E31" s="353"/>
+      <c r="F31" s="353"/>
+      <c r="G31" s="353"/>
+      <c r="H31" s="353"/>
+      <c r="I31" s="353"/>
+      <c r="J31" s="353"/>
+      <c r="K31" s="353"/>
+      <c r="L31" s="354"/>
       <c r="M31" s="131"/>
-      <c r="N31" s="341" t="s">
+      <c r="N31" s="332" t="s">
         <v>87</v>
       </c>
-      <c r="O31" s="342"/>
+      <c r="O31" s="333"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
         <v>653546.96149999998</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="335"/>
-      <c r="C32" s="336"/>
-      <c r="D32" s="336"/>
-      <c r="E32" s="336"/>
-      <c r="F32" s="336"/>
-      <c r="G32" s="336"/>
-      <c r="H32" s="336"/>
-      <c r="I32" s="336"/>
-      <c r="J32" s="336"/>
-      <c r="K32" s="336"/>
-      <c r="L32" s="337"/>
+      <c r="B32" s="352"/>
+      <c r="C32" s="353"/>
+      <c r="D32" s="353"/>
+      <c r="E32" s="353"/>
+      <c r="F32" s="353"/>
+      <c r="G32" s="353"/>
+      <c r="H32" s="353"/>
+      <c r="I32" s="353"/>
+      <c r="J32" s="353"/>
+      <c r="K32" s="353"/>
+      <c r="L32" s="354"/>
       <c r="M32" s="131"/>
       <c r="N32" s="136" t="s">
         <v>61</v>
@@ -10917,39 +10920,39 @@
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="335"/>
-      <c r="C33" s="336"/>
-      <c r="D33" s="336"/>
-      <c r="E33" s="336"/>
-      <c r="F33" s="336"/>
-      <c r="G33" s="336"/>
-      <c r="H33" s="336"/>
-      <c r="I33" s="336"/>
-      <c r="J33" s="336"/>
-      <c r="K33" s="336"/>
-      <c r="L33" s="337"/>
+      <c r="B33" s="352"/>
+      <c r="C33" s="353"/>
+      <c r="D33" s="353"/>
+      <c r="E33" s="353"/>
+      <c r="F33" s="353"/>
+      <c r="G33" s="353"/>
+      <c r="H33" s="353"/>
+      <c r="I33" s="353"/>
+      <c r="J33" s="353"/>
+      <c r="K33" s="353"/>
+      <c r="L33" s="354"/>
       <c r="M33" s="131"/>
-      <c r="N33" s="360" t="s">
+      <c r="N33" s="330" t="s">
         <v>76</v>
       </c>
-      <c r="O33" s="361"/>
+      <c r="O33" s="331"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
         <v>810895.9445508474</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="338"/>
-      <c r="C34" s="339"/>
-      <c r="D34" s="339"/>
-      <c r="E34" s="339"/>
-      <c r="F34" s="339"/>
-      <c r="G34" s="339"/>
-      <c r="H34" s="339"/>
-      <c r="I34" s="339"/>
-      <c r="J34" s="339"/>
-      <c r="K34" s="339"/>
-      <c r="L34" s="340"/>
+      <c r="B34" s="355"/>
+      <c r="C34" s="356"/>
+      <c r="D34" s="356"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
+      <c r="G34" s="356"/>
+      <c r="H34" s="356"/>
+      <c r="I34" s="356"/>
+      <c r="J34" s="356"/>
+      <c r="K34" s="356"/>
+      <c r="L34" s="357"/>
       <c r="M34" s="99"/>
       <c r="N34" s="138" t="s">
         <v>83</v>
@@ -10964,10 +10967,10 @@
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N35" s="343" t="s">
+      <c r="N35" s="358" t="s">
         <v>88</v>
       </c>
-      <c r="O35" s="344"/>
+      <c r="O35" s="359"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
         <v>814950.42427360162</v>
@@ -10977,15 +10980,15 @@
       <c r="B36" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="328"/>
-      <c r="D36" s="328"/>
-      <c r="E36" s="328"/>
-      <c r="F36" s="328"/>
-      <c r="G36" s="328"/>
-      <c r="H36" s="328"/>
-      <c r="I36" s="329"/>
-      <c r="J36" s="330"/>
-      <c r="K36" s="331"/>
+      <c r="C36" s="344"/>
+      <c r="D36" s="344"/>
+      <c r="E36" s="344"/>
+      <c r="F36" s="344"/>
+      <c r="G36" s="344"/>
+      <c r="H36" s="344"/>
+      <c r="I36" s="345"/>
+      <c r="J36" s="346"/>
+      <c r="K36" s="347"/>
     </row>
     <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="2:16" x14ac:dyDescent="0.35">
@@ -10996,27 +10999,17 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="48">
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N8:P8"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="N10:P10"/>
@@ -11033,17 +11026,27 @@
     <mergeCell ref="N28:O28"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E14:F14"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <dataValidations count="3">
@@ -11098,28 +11101,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:18 16382:16383" ht="21" x14ac:dyDescent="0.5">
-      <c r="A2" s="358" t="s">
+      <c r="A2" s="341" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="358"/>
-      <c r="C2" s="358"/>
+      <c r="B2" s="341"/>
+      <c r="C2" s="341"/>
     </row>
     <row r="3" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="326" t="s">
+      <c r="A3" s="342" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="326"/>
-      <c r="C3" s="326"/>
+      <c r="B3" s="342"/>
+      <c r="C3" s="342"/>
       <c r="F3" s="85"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="325" t="s">
+      <c r="J3" s="326" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="325"/>
-      <c r="L3" s="325"/>
-      <c r="M3" s="326"/>
-      <c r="N3" s="326"/>
-      <c r="O3" s="326"/>
+      <c r="K3" s="326"/>
+      <c r="L3" s="326"/>
+      <c r="M3" s="342"/>
+      <c r="N3" s="342"/>
+      <c r="O3" s="342"/>
       <c r="Q3" s="85"/>
       <c r="R3" s="1"/>
       <c r="XFB3" t="s">
@@ -11130,24 +11133,24 @@
       </c>
     </row>
     <row r="4" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="326" t="s">
+      <c r="A4" s="342" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="326"/>
-      <c r="C4" s="326"/>
+      <c r="B4" s="342"/>
+      <c r="C4" s="342"/>
       <c r="F4" s="85"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="325" t="s">
+      <c r="J4" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="325"/>
-      <c r="L4" s="325"/>
-      <c r="M4" s="327">
+      <c r="K4" s="326"/>
+      <c r="L4" s="326"/>
+      <c r="M4" s="368">
         <f ca="1">TODAY()+1</f>
-        <v>46224</v>
-      </c>
-      <c r="N4" s="327"/>
-      <c r="O4" s="327"/>
+        <v>46225</v>
+      </c>
+      <c r="N4" s="368"/>
+      <c r="O4" s="368"/>
       <c r="Q4" s="85"/>
       <c r="R4" s="1"/>
       <c r="XFB4" s="87" t="s">
@@ -11158,45 +11161,45 @@
       </c>
     </row>
     <row r="5" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="359" t="s">
+      <c r="A5" s="343" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
+      <c r="B5" s="343"/>
+      <c r="C5" s="343"/>
       <c r="F5" s="85"/>
       <c r="G5" s="1"/>
-      <c r="J5" s="325" t="s">
+      <c r="J5" s="326" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="325"/>
-      <c r="L5" s="325"/>
-      <c r="M5" s="327">
+      <c r="K5" s="326"/>
+      <c r="L5" s="326"/>
+      <c r="M5" s="368">
         <f ca="1">M4-1</f>
-        <v>46223</v>
-      </c>
-      <c r="N5" s="326"/>
-      <c r="O5" s="326"/>
+        <v>46224</v>
+      </c>
+      <c r="N5" s="342"/>
+      <c r="O5" s="342"/>
       <c r="Q5" s="85"/>
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="325" t="s">
+      <c r="A6" s="326" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="325"/>
-      <c r="C6" s="325"/>
+      <c r="B6" s="326"/>
+      <c r="C6" s="326"/>
       <c r="F6" s="85"/>
       <c r="G6" s="86"/>
-      <c r="J6" s="325" t="s">
+      <c r="J6" s="326" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="325"/>
-      <c r="L6" s="325"/>
-      <c r="M6" s="324" t="s">
+      <c r="K6" s="326"/>
+      <c r="L6" s="326"/>
+      <c r="M6" s="348" t="s">
         <v>62</v>
       </c>
-      <c r="N6" s="324"/>
-      <c r="O6" s="324"/>
+      <c r="N6" s="348"/>
+      <c r="O6" s="348"/>
       <c r="Q6" s="85"/>
       <c r="R6" s="86"/>
       <c r="XFB6" t="s">
@@ -11207,23 +11210,23 @@
       </c>
     </row>
     <row r="7" spans="1:18 16382:16383" s="87" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="325" t="s">
+      <c r="A7" s="326" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="325"/>
-      <c r="C7" s="325"/>
+      <c r="B7" s="326"/>
+      <c r="C7" s="326"/>
       <c r="F7" s="85"/>
       <c r="G7" s="86"/>
-      <c r="J7" s="325" t="s">
+      <c r="J7" s="326" t="s">
         <v>66</v>
       </c>
-      <c r="K7" s="325"/>
-      <c r="L7" s="325"/>
-      <c r="M7" s="324" t="s">
+      <c r="K7" s="326"/>
+      <c r="L7" s="326"/>
+      <c r="M7" s="348" t="s">
         <v>70</v>
       </c>
-      <c r="N7" s="324"/>
-      <c r="O7" s="324"/>
+      <c r="N7" s="348"/>
+      <c r="O7" s="348"/>
       <c r="Q7" s="85"/>
       <c r="R7" s="86"/>
       <c r="XFB7" t="s">
@@ -11234,44 +11237,44 @@
       </c>
     </row>
     <row r="8" spans="1:18 16382:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="366" t="s">
+      <c r="A8" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="366"/>
-      <c r="C8" s="366"/>
+      <c r="B8" s="327"/>
+      <c r="C8" s="327"/>
       <c r="F8" s="85"/>
       <c r="G8" s="86"/>
-      <c r="J8" s="325" t="s">
+      <c r="J8" s="326" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="325"/>
-      <c r="L8" s="325"/>
-      <c r="M8" s="324" t="s">
+      <c r="K8" s="326"/>
+      <c r="L8" s="326"/>
+      <c r="M8" s="348" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="324"/>
-      <c r="O8" s="324"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="348"/>
       <c r="Q8" s="85"/>
       <c r="R8" s="86"/>
     </row>
     <row r="9" spans="1:18 16382:16383" x14ac:dyDescent="0.35">
-      <c r="A9" s="366" t="s">
+      <c r="A9" s="327" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="366"/>
-      <c r="C9" s="366"/>
+      <c r="B9" s="327"/>
+      <c r="C9" s="327"/>
       <c r="F9" s="85"/>
       <c r="G9" s="86"/>
-      <c r="J9" s="325" t="s">
+      <c r="J9" s="326" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="325"/>
-      <c r="L9" s="325"/>
-      <c r="M9" s="324" t="s">
+      <c r="K9" s="326"/>
+      <c r="L9" s="326"/>
+      <c r="M9" s="348" t="s">
         <v>104</v>
       </c>
-      <c r="N9" s="324"/>
-      <c r="O9" s="324"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="348"/>
       <c r="Q9" s="85"/>
       <c r="R9" s="86"/>
       <c r="XFC9" t="s">
@@ -11279,23 +11282,23 @@
       </c>
     </row>
     <row r="10" spans="1:18 16382:16383" x14ac:dyDescent="0.35">
-      <c r="A10" s="366" t="s">
+      <c r="A10" s="327" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="366"/>
-      <c r="C10" s="366"/>
+      <c r="B10" s="327"/>
+      <c r="C10" s="327"/>
       <c r="F10" s="85"/>
       <c r="G10" s="1"/>
-      <c r="J10" s="325" t="s">
+      <c r="J10" s="326" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="325"/>
-      <c r="L10" s="325"/>
-      <c r="M10" s="326" t="s">
+      <c r="K10" s="326"/>
+      <c r="L10" s="326"/>
+      <c r="M10" s="342" t="s">
         <v>47</v>
       </c>
-      <c r="N10" s="326"/>
-      <c r="O10" s="326"/>
+      <c r="N10" s="342"/>
+      <c r="O10" s="342"/>
       <c r="Q10" s="85"/>
       <c r="R10" s="1"/>
       <c r="XFC10" t="s">
@@ -11315,16 +11318,16 @@
       </c>
       <c r="F11" s="85"/>
       <c r="G11" s="1"/>
-      <c r="J11" s="325" t="s">
+      <c r="J11" s="326" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="325"/>
-      <c r="L11" s="325"/>
-      <c r="M11" s="326" t="s">
+      <c r="K11" s="326"/>
+      <c r="L11" s="326"/>
+      <c r="M11" s="342" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="326"/>
-      <c r="O11" s="326"/>
+      <c r="N11" s="342"/>
+      <c r="O11" s="342"/>
       <c r="P11" s="250"/>
       <c r="Q11" s="85"/>
       <c r="R11" s="1"/>
@@ -11342,14 +11345,14 @@
       </c>
       <c r="F12" s="85"/>
       <c r="G12" s="1"/>
-      <c r="J12" s="325" t="s">
+      <c r="J12" s="326" t="s">
         <v>50</v>
       </c>
-      <c r="K12" s="325"/>
-      <c r="L12" s="325"/>
-      <c r="M12" s="326"/>
-      <c r="N12" s="326"/>
-      <c r="O12" s="326"/>
+      <c r="K12" s="326"/>
+      <c r="L12" s="326"/>
+      <c r="M12" s="342"/>
+      <c r="N12" s="342"/>
+      <c r="O12" s="342"/>
       <c r="Q12" s="85"/>
       <c r="R12" s="1"/>
       <c r="XFC12" t="s">
@@ -11366,11 +11369,11 @@
       </c>
     </row>
     <row r="14" spans="1:18 16382:16383" ht="20.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="347" t="s">
+      <c r="A14" s="360" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="348"/>
-      <c r="C14" s="364" t="s">
+      <c r="B14" s="337"/>
+      <c r="C14" s="324" t="s">
         <v>90</v>
       </c>
       <c r="D14" s="88" t="s">
@@ -11382,18 +11385,18 @@
       <c r="F14" s="115" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="362" t="s">
+      <c r="G14" s="334" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="346"/>
-      <c r="I14" s="351" t="s">
+      <c r="H14" s="336"/>
+      <c r="I14" s="362" t="s">
         <v>77</v>
       </c>
-      <c r="J14" s="345" t="s">
+      <c r="J14" s="335" t="s">
         <v>55</v>
       </c>
-      <c r="K14" s="346"/>
-      <c r="L14" s="351" t="s">
+      <c r="K14" s="336"/>
+      <c r="L14" s="362" t="s">
         <v>84</v>
       </c>
       <c r="M14" s="130" t="s">
@@ -11410,9 +11413,9 @@
       </c>
     </row>
     <row r="15" spans="1:18 16382:16383" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="349"/>
-      <c r="B15" s="350"/>
-      <c r="C15" s="365"/>
+      <c r="A15" s="361"/>
+      <c r="B15" s="338"/>
+      <c r="C15" s="325"/>
       <c r="D15" s="90" t="s">
         <v>57</v>
       </c>
@@ -11428,14 +11431,14 @@
       <c r="H15" s="146" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="352"/>
+      <c r="I15" s="340"/>
       <c r="J15" s="144" t="s">
         <v>39</v>
       </c>
       <c r="K15" s="145" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="352"/>
+      <c r="L15" s="340"/>
       <c r="M15" s="132">
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
@@ -11957,17 +11960,17 @@
       </c>
     </row>
     <row r="25" spans="1:18 16383:16383" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="357">
+      <c r="A25" s="367">
         <f>COUNT(A16:A24)</f>
         <v>0</v>
       </c>
-      <c r="B25" s="355"/>
-      <c r="C25" s="355" t="s">
+      <c r="B25" s="365"/>
+      <c r="C25" s="365" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="355"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="356"/>
+      <c r="D25" s="365"/>
+      <c r="E25" s="365"/>
+      <c r="F25" s="366"/>
       <c r="G25" s="117">
         <f t="shared" ref="G25:L25" si="7">SUM(G16:G24)</f>
         <v>0</v>
@@ -12033,99 +12036,99 @@
       <c r="H27" s="94"/>
     </row>
     <row r="28" spans="1:18 16383:16383" x14ac:dyDescent="0.35">
-      <c r="B28" s="332" t="s">
+      <c r="B28" s="349" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="333"/>
-      <c r="D28" s="333"/>
-      <c r="E28" s="333"/>
-      <c r="F28" s="333"/>
-      <c r="G28" s="333"/>
-      <c r="H28" s="333"/>
-      <c r="I28" s="333"/>
-      <c r="J28" s="333"/>
-      <c r="K28" s="334"/>
-      <c r="M28" s="353" t="s">
+      <c r="C28" s="350"/>
+      <c r="D28" s="350"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
+      <c r="G28" s="350"/>
+      <c r="H28" s="350"/>
+      <c r="I28" s="350"/>
+      <c r="J28" s="350"/>
+      <c r="K28" s="351"/>
+      <c r="M28" s="363" t="s">
         <v>60</v>
       </c>
-      <c r="N28" s="354"/>
+      <c r="N28" s="364"/>
       <c r="O28" s="139">
         <f>I25</f>
         <v>1452.8</v>
       </c>
     </row>
     <row r="29" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="335"/>
-      <c r="C29" s="336"/>
-      <c r="D29" s="336"/>
-      <c r="E29" s="336"/>
-      <c r="F29" s="336"/>
-      <c r="G29" s="336"/>
-      <c r="H29" s="336"/>
-      <c r="I29" s="336"/>
-      <c r="J29" s="336"/>
-      <c r="K29" s="337"/>
-      <c r="M29" s="341" t="s">
+      <c r="B29" s="352"/>
+      <c r="C29" s="353"/>
+      <c r="D29" s="353"/>
+      <c r="E29" s="353"/>
+      <c r="F29" s="353"/>
+      <c r="G29" s="353"/>
+      <c r="H29" s="353"/>
+      <c r="I29" s="353"/>
+      <c r="J29" s="353"/>
+      <c r="K29" s="354"/>
+      <c r="M29" s="332" t="s">
         <v>85</v>
       </c>
-      <c r="N29" s="342"/>
+      <c r="N29" s="333"/>
       <c r="O29" s="140">
         <f>K25</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="335"/>
-      <c r="C30" s="336"/>
-      <c r="D30" s="336"/>
-      <c r="E30" s="336"/>
-      <c r="F30" s="336"/>
-      <c r="G30" s="336"/>
-      <c r="H30" s="336"/>
-      <c r="I30" s="336"/>
-      <c r="J30" s="336"/>
-      <c r="K30" s="337"/>
-      <c r="M30" s="341" t="s">
+      <c r="B30" s="352"/>
+      <c r="C30" s="353"/>
+      <c r="D30" s="353"/>
+      <c r="E30" s="353"/>
+      <c r="F30" s="353"/>
+      <c r="G30" s="353"/>
+      <c r="H30" s="353"/>
+      <c r="I30" s="353"/>
+      <c r="J30" s="353"/>
+      <c r="K30" s="354"/>
+      <c r="M30" s="332" t="s">
         <v>86</v>
       </c>
-      <c r="N30" s="342"/>
+      <c r="N30" s="333"/>
       <c r="O30" s="140">
         <f>J25</f>
         <v>50.848000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="335"/>
-      <c r="C31" s="336"/>
-      <c r="D31" s="336"/>
-      <c r="E31" s="336"/>
-      <c r="F31" s="336"/>
-      <c r="G31" s="336"/>
-      <c r="H31" s="336"/>
-      <c r="I31" s="336"/>
-      <c r="J31" s="336"/>
-      <c r="K31" s="337"/>
+      <c r="B31" s="352"/>
+      <c r="C31" s="353"/>
+      <c r="D31" s="353"/>
+      <c r="E31" s="353"/>
+      <c r="F31" s="353"/>
+      <c r="G31" s="353"/>
+      <c r="H31" s="353"/>
+      <c r="I31" s="353"/>
+      <c r="J31" s="353"/>
+      <c r="K31" s="354"/>
       <c r="L31" s="131"/>
-      <c r="M31" s="341" t="s">
+      <c r="M31" s="332" t="s">
         <v>87</v>
       </c>
-      <c r="N31" s="342"/>
+      <c r="N31" s="333"/>
       <c r="O31" s="140">
         <f>O28-O29-O30</f>
         <v>1401.952</v>
       </c>
     </row>
     <row r="32" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="335"/>
-      <c r="C32" s="336"/>
-      <c r="D32" s="336"/>
-      <c r="E32" s="336"/>
-      <c r="F32" s="336"/>
-      <c r="G32" s="336"/>
-      <c r="H32" s="336"/>
-      <c r="I32" s="336"/>
-      <c r="J32" s="336"/>
-      <c r="K32" s="337"/>
+      <c r="B32" s="352"/>
+      <c r="C32" s="353"/>
+      <c r="D32" s="353"/>
+      <c r="E32" s="353"/>
+      <c r="F32" s="353"/>
+      <c r="G32" s="353"/>
+      <c r="H32" s="353"/>
+      <c r="I32" s="353"/>
+      <c r="J32" s="353"/>
+      <c r="K32" s="354"/>
       <c r="L32" s="131"/>
       <c r="M32" s="136" t="s">
         <v>61</v>
@@ -12140,37 +12143,37 @@
       </c>
     </row>
     <row r="33" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="335"/>
-      <c r="C33" s="336"/>
-      <c r="D33" s="336"/>
-      <c r="E33" s="336"/>
-      <c r="F33" s="336"/>
-      <c r="G33" s="336"/>
-      <c r="H33" s="336"/>
-      <c r="I33" s="336"/>
-      <c r="J33" s="336"/>
-      <c r="K33" s="337"/>
+      <c r="B33" s="352"/>
+      <c r="C33" s="353"/>
+      <c r="D33" s="353"/>
+      <c r="E33" s="353"/>
+      <c r="F33" s="353"/>
+      <c r="G33" s="353"/>
+      <c r="H33" s="353"/>
+      <c r="I33" s="353"/>
+      <c r="J33" s="353"/>
+      <c r="K33" s="354"/>
       <c r="L33" s="131"/>
-      <c r="M33" s="360" t="s">
+      <c r="M33" s="330" t="s">
         <v>76</v>
       </c>
-      <c r="N33" s="361"/>
+      <c r="N33" s="331"/>
       <c r="O33" s="140">
         <f>O31+O32</f>
         <v>1710.3814400000001</v>
       </c>
     </row>
     <row r="34" spans="2:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="338"/>
-      <c r="C34" s="339"/>
-      <c r="D34" s="339"/>
-      <c r="E34" s="339"/>
-      <c r="F34" s="339"/>
-      <c r="G34" s="339"/>
-      <c r="H34" s="339"/>
-      <c r="I34" s="339"/>
-      <c r="J34" s="339"/>
-      <c r="K34" s="340"/>
+      <c r="B34" s="355"/>
+      <c r="C34" s="356"/>
+      <c r="D34" s="356"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
+      <c r="G34" s="356"/>
+      <c r="H34" s="356"/>
+      <c r="I34" s="356"/>
+      <c r="J34" s="356"/>
+      <c r="K34" s="357"/>
       <c r="L34" s="99"/>
       <c r="M34" s="138" t="s">
         <v>83</v>
@@ -12185,10 +12188,10 @@
       </c>
     </row>
     <row r="35" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="M35" s="343" t="s">
+      <c r="M35" s="358" t="s">
         <v>88</v>
       </c>
-      <c r="N35" s="344"/>
+      <c r="N35" s="359"/>
       <c r="O35" s="141">
         <f>O28-O29+O31+O34</f>
         <v>2897.511536</v>
@@ -12198,53 +12201,19 @@
       <c r="B36" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="328"/>
-      <c r="D36" s="328"/>
-      <c r="E36" s="328"/>
-      <c r="F36" s="328"/>
-      <c r="G36" s="328"/>
-      <c r="H36" s="328"/>
-      <c r="I36" s="329"/>
+      <c r="C36" s="344"/>
+      <c r="D36" s="344"/>
+      <c r="E36" s="344"/>
+      <c r="F36" s="344"/>
+      <c r="G36" s="344"/>
+      <c r="H36" s="344"/>
+      <c r="I36" s="345"/>
       <c r="J36" s="261"/>
     </row>
     <row r="37" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="45">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="L14:L15"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="J14:K14"/>
@@ -12256,6 +12225,40 @@
     <mergeCell ref="M30:N30"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="M33:N33"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M9:O9" xr:uid="{C3716279-191D-4737-BAA3-4E59961C8ADB}">
@@ -12309,7 +12312,7 @@
       <c r="C1" s="316" t="s">
         <v>438</v>
       </c>
-      <c r="D1" s="372" t="s">
+      <c r="D1" s="371" t="s">
         <v>439</v>
       </c>
       <c r="E1" s="316" t="s">
@@ -12320,23 +12323,23 @@
         <v>440</v>
       </c>
       <c r="H1" s="317"/>
-      <c r="I1" s="373" t="s">
+      <c r="I1" s="378" t="s">
         <v>441</v>
       </c>
-      <c r="J1" s="373"/>
-      <c r="K1" s="373" t="s">
+      <c r="J1" s="378"/>
+      <c r="K1" s="378" t="s">
         <v>442</v>
       </c>
-      <c r="L1" s="373"/>
-      <c r="M1" s="369" t="s">
+      <c r="L1" s="378"/>
+      <c r="M1" s="373" t="s">
         <v>484</v>
       </c>
-      <c r="N1" s="370"/>
-      <c r="O1" s="371"/>
+      <c r="N1" s="374"/>
+      <c r="O1" s="375"/>
     </row>
     <row r="2" spans="3:24" ht="29" x14ac:dyDescent="0.35">
       <c r="C2" s="316"/>
-      <c r="D2" s="372"/>
+      <c r="D2" s="371"/>
       <c r="E2" s="168" t="s">
         <v>36</v>
       </c>
@@ -12510,13 +12513,13 @@
       </c>
     </row>
     <row r="6" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C6" s="374" t="s">
+      <c r="C6" s="376" t="s">
         <v>476</v>
       </c>
-      <c r="D6" s="374"/>
-      <c r="E6" s="374"/>
-      <c r="F6" s="374"/>
-      <c r="G6" s="374"/>
+      <c r="D6" s="376"/>
+      <c r="E6" s="376"/>
+      <c r="F6" s="376"/>
+      <c r="G6" s="376"/>
       <c r="T6" s="257" t="s">
         <v>487</v>
       </c>
@@ -12531,11 +12534,11 @@
       <c r="D7" s="315" t="s">
         <v>439</v>
       </c>
-      <c r="E7" s="376" t="s">
+      <c r="E7" s="372" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="376"/>
-      <c r="G7" s="377" t="s">
+      <c r="F7" s="372"/>
+      <c r="G7" s="370" t="s">
         <v>440</v>
       </c>
       <c r="H7" s="317"/>
@@ -12547,27 +12550,27 @@
         <v>442</v>
       </c>
       <c r="L7" s="319"/>
-      <c r="M7" s="369" t="s">
+      <c r="M7" s="373" t="s">
         <v>484</v>
       </c>
-      <c r="N7" s="370"/>
-      <c r="O7" s="371"/>
+      <c r="N7" s="374"/>
+      <c r="O7" s="375"/>
       <c r="P7" s="256" t="s">
         <v>475</v>
       </c>
       <c r="Q7" s="242" t="s">
         <v>473</v>
       </c>
-      <c r="R7" s="372" t="s">
+      <c r="R7" s="371" t="s">
         <v>475</v>
       </c>
-      <c r="S7" s="372" t="s">
+      <c r="S7" s="371" t="s">
         <v>485</v>
       </c>
-      <c r="T7" s="378" t="s">
+      <c r="T7" s="369" t="s">
         <v>486</v>
       </c>
-      <c r="U7" s="378" t="s">
+      <c r="U7" s="369" t="s">
         <v>486</v>
       </c>
     </row>
@@ -12613,10 +12616,10 @@
       <c r="Q8" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="R8" s="372"/>
-      <c r="S8" s="372"/>
-      <c r="T8" s="377"/>
-      <c r="U8" s="377"/>
+      <c r="R8" s="371"/>
+      <c r="S8" s="371"/>
+      <c r="T8" s="370"/>
+      <c r="U8" s="370"/>
     </row>
     <row r="9" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C9" s="166" t="s">
@@ -12823,13 +12826,13 @@
       </c>
     </row>
     <row r="12" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="375" t="s">
+      <c r="C12" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="D12" s="375"/>
-      <c r="E12" s="375"/>
-      <c r="F12" s="375"/>
-      <c r="G12" s="375"/>
+      <c r="D12" s="377"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
+      <c r="G12" s="377"/>
     </row>
     <row r="13" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C13" s="312" t="s">
@@ -12854,27 +12857,27 @@
         <v>442</v>
       </c>
       <c r="L13" s="319"/>
-      <c r="M13" s="369" t="s">
+      <c r="M13" s="373" t="s">
         <v>484</v>
       </c>
-      <c r="N13" s="370"/>
-      <c r="O13" s="371"/>
+      <c r="N13" s="374"/>
+      <c r="O13" s="375"/>
       <c r="P13" s="256" t="s">
         <v>475</v>
       </c>
       <c r="Q13" s="242" t="s">
         <v>473</v>
       </c>
-      <c r="R13" s="372" t="s">
+      <c r="R13" s="371" t="s">
         <v>475</v>
       </c>
-      <c r="S13" s="372" t="s">
+      <c r="S13" s="371" t="s">
         <v>485</v>
       </c>
-      <c r="T13" s="378" t="s">
+      <c r="T13" s="369" t="s">
         <v>486</v>
       </c>
-      <c r="U13" s="378" t="s">
+      <c r="U13" s="369" t="s">
         <v>486</v>
       </c>
     </row>
@@ -12920,10 +12923,10 @@
       <c r="Q14" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="R14" s="372"/>
-      <c r="S14" s="372"/>
-      <c r="T14" s="377"/>
-      <c r="U14" s="377"/>
+      <c r="R14" s="371"/>
+      <c r="S14" s="371"/>
+      <c r="T14" s="370"/>
+      <c r="U14" s="370"/>
     </row>
     <row r="15" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C15" s="166" t="s">
@@ -13130,13 +13133,13 @@
       </c>
     </row>
     <row r="19" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C19" s="374" t="s">
+      <c r="C19" s="376" t="s">
         <v>478</v>
       </c>
-      <c r="D19" s="374"/>
-      <c r="E19" s="374"/>
-      <c r="F19" s="374"/>
-      <c r="G19" s="374"/>
+      <c r="D19" s="376"/>
+      <c r="E19" s="376"/>
+      <c r="F19" s="376"/>
+      <c r="G19" s="376"/>
     </row>
     <row r="20" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C20" s="312" t="s">
@@ -13161,27 +13164,27 @@
         <v>442</v>
       </c>
       <c r="L20" s="319"/>
-      <c r="M20" s="369" t="s">
+      <c r="M20" s="373" t="s">
         <v>484</v>
       </c>
-      <c r="N20" s="370"/>
-      <c r="O20" s="371"/>
+      <c r="N20" s="374"/>
+      <c r="O20" s="375"/>
       <c r="P20" s="256" t="s">
         <v>475</v>
       </c>
       <c r="Q20" s="242" t="s">
         <v>473</v>
       </c>
-      <c r="R20" s="372" t="s">
+      <c r="R20" s="371" t="s">
         <v>475</v>
       </c>
-      <c r="S20" s="372" t="s">
+      <c r="S20" s="371" t="s">
         <v>485</v>
       </c>
-      <c r="T20" s="378" t="s">
+      <c r="T20" s="369" t="s">
         <v>486</v>
       </c>
-      <c r="U20" s="378" t="s">
+      <c r="U20" s="369" t="s">
         <v>486</v>
       </c>
     </row>
@@ -13227,10 +13230,10 @@
       <c r="Q21" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="R21" s="372"/>
-      <c r="S21" s="372"/>
-      <c r="T21" s="377"/>
-      <c r="U21" s="377"/>
+      <c r="R21" s="371"/>
+      <c r="S21" s="371"/>
+      <c r="T21" s="370"/>
+      <c r="U21" s="370"/>
     </row>
     <row r="22" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C22" s="166" t="s">
@@ -13455,13 +13458,13 @@
       <c r="R25" s="164"/>
     </row>
     <row r="26" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C26" s="374" t="s">
+      <c r="C26" s="376" t="s">
         <v>479</v>
       </c>
-      <c r="D26" s="374"/>
-      <c r="E26" s="374"/>
-      <c r="F26" s="374"/>
-      <c r="G26" s="374"/>
+      <c r="D26" s="376"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
+      <c r="G26" s="376"/>
     </row>
     <row r="27" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C27" s="312" t="s">
@@ -13486,27 +13489,27 @@
         <v>442</v>
       </c>
       <c r="L27" s="319"/>
-      <c r="M27" s="369" t="s">
+      <c r="M27" s="373" t="s">
         <v>484</v>
       </c>
-      <c r="N27" s="370"/>
-      <c r="O27" s="371"/>
+      <c r="N27" s="374"/>
+      <c r="O27" s="375"/>
       <c r="P27" s="256" t="s">
         <v>475</v>
       </c>
       <c r="Q27" s="242" t="s">
         <v>473</v>
       </c>
-      <c r="R27" s="372" t="s">
+      <c r="R27" s="371" t="s">
         <v>475</v>
       </c>
-      <c r="S27" s="372" t="s">
+      <c r="S27" s="371" t="s">
         <v>485</v>
       </c>
-      <c r="T27" s="378" t="s">
+      <c r="T27" s="369" t="s">
         <v>486</v>
       </c>
-      <c r="U27" s="378" t="s">
+      <c r="U27" s="369" t="s">
         <v>486</v>
       </c>
     </row>
@@ -13552,10 +13555,10 @@
       <c r="Q28" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="R28" s="372"/>
-      <c r="S28" s="372"/>
-      <c r="T28" s="377"/>
-      <c r="U28" s="377"/>
+      <c r="R28" s="371"/>
+      <c r="S28" s="371"/>
+      <c r="T28" s="370"/>
+      <c r="U28" s="370"/>
     </row>
     <row r="29" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C29" s="166" t="s">
@@ -13763,29 +13766,22 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="R13:R14"/>
     <mergeCell ref="M27:O27"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="C26:G26"/>
@@ -13802,22 +13798,29 @@
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="T20:T21"/>
   </mergeCells>
   <conditionalFormatting sqref="C1 C3:C5">
     <cfRule type="cellIs" dxfId="44" priority="1" stopIfTrue="1" operator="lessThan">
@@ -13891,7 +13894,7 @@
       <c r="B1" s="316" t="s">
         <v>438</v>
       </c>
-      <c r="C1" s="372" t="s">
+      <c r="C1" s="371" t="s">
         <v>439</v>
       </c>
       <c r="D1" s="316" t="s">
@@ -13902,23 +13905,23 @@
         <v>440</v>
       </c>
       <c r="G1" s="317"/>
-      <c r="H1" s="373" t="s">
+      <c r="H1" s="378" t="s">
         <v>441</v>
       </c>
-      <c r="I1" s="373"/>
-      <c r="J1" s="373" t="s">
+      <c r="I1" s="378"/>
+      <c r="J1" s="378" t="s">
         <v>442</v>
       </c>
-      <c r="K1" s="373"/>
-      <c r="L1" s="369" t="s">
+      <c r="K1" s="378"/>
+      <c r="L1" s="373" t="s">
         <v>484</v>
       </c>
-      <c r="M1" s="370"/>
-      <c r="N1" s="371"/>
+      <c r="M1" s="374"/>
+      <c r="N1" s="375"/>
     </row>
     <row r="2" spans="2:17" ht="29" x14ac:dyDescent="0.35">
       <c r="B2" s="316"/>
-      <c r="C2" s="372"/>
+      <c r="C2" s="371"/>
       <c r="D2" s="168" t="s">
         <v>36</v>
       </c>
@@ -14173,7 +14176,7 @@
       <c r="E5" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="380" t="s">
+      <c r="F5" s="381" t="s">
         <v>124</v>
       </c>
       <c r="G5" s="149" t="s">
@@ -14890,7 +14893,7 @@
       <c r="E59" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F59" s="381" t="s">
+      <c r="F59" s="380" t="s">
         <v>193</v>
       </c>
       <c r="G59" s="160" t="s">
@@ -14904,7 +14907,7 @@
       <c r="E60" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F60" s="381"/>
+      <c r="F60" s="380"/>
       <c r="G60" s="160" t="s">
         <v>195</v>
       </c>
@@ -14916,7 +14919,7 @@
       <c r="E61" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F61" s="381"/>
+      <c r="F61" s="380"/>
       <c r="G61" s="160" t="s">
         <v>196</v>
       </c>
@@ -14928,7 +14931,7 @@
       <c r="E62" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F62" s="381"/>
+      <c r="F62" s="380"/>
       <c r="G62" s="160" t="s">
         <v>197</v>
       </c>
@@ -14940,7 +14943,7 @@
       <c r="E63" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F63" s="381"/>
+      <c r="F63" s="380"/>
       <c r="G63" s="160" t="s">
         <v>198</v>
       </c>
@@ -14952,7 +14955,7 @@
       <c r="E64" s="159" t="s">
         <v>192</v>
       </c>
-      <c r="F64" s="381"/>
+      <c r="F64" s="380"/>
       <c r="G64" s="162" t="s">
         <v>199</v>
       </c>
@@ -15630,7 +15633,7 @@
       <c r="E119" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F119" s="381" t="s">
+      <c r="F119" s="380" t="s">
         <v>270</v>
       </c>
       <c r="G119" s="160" t="s">
@@ -15644,7 +15647,7 @@
       <c r="E120" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F120" s="381"/>
+      <c r="F120" s="380"/>
       <c r="G120" s="160" t="s">
         <v>272</v>
       </c>
@@ -15656,7 +15659,7 @@
       <c r="E121" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F121" s="381"/>
+      <c r="F121" s="380"/>
       <c r="G121" s="160" t="s">
         <v>273</v>
       </c>
@@ -15668,7 +15671,7 @@
       <c r="E122" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F122" s="381"/>
+      <c r="F122" s="380"/>
       <c r="G122" s="160" t="s">
         <v>274</v>
       </c>
@@ -15680,7 +15683,7 @@
       <c r="E123" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F123" s="381"/>
+      <c r="F123" s="380"/>
       <c r="G123" s="160" t="s">
         <v>275</v>
       </c>
@@ -15692,7 +15695,7 @@
       <c r="E124" s="159" t="s">
         <v>269</v>
       </c>
-      <c r="F124" s="381"/>
+      <c r="F124" s="380"/>
       <c r="G124" s="162" t="s">
         <v>276</v>
       </c>
@@ -17110,7 +17113,7 @@
       <c r="E239" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F239" s="381" t="s">
+      <c r="F239" s="380" t="s">
         <v>429</v>
       </c>
       <c r="G239" s="160" t="s">
@@ -17124,7 +17127,7 @@
       <c r="E240" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F240" s="381"/>
+      <c r="F240" s="380"/>
       <c r="G240" s="160" t="s">
         <v>431</v>
       </c>
@@ -17136,7 +17139,7 @@
       <c r="E241" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F241" s="381"/>
+      <c r="F241" s="380"/>
       <c r="G241" s="160" t="s">
         <v>432</v>
       </c>
@@ -17148,7 +17151,7 @@
       <c r="E242" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F242" s="381"/>
+      <c r="F242" s="380"/>
       <c r="G242" s="160" t="s">
         <v>433</v>
       </c>
@@ -17160,7 +17163,7 @@
       <c r="E243" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F243" s="381"/>
+      <c r="F243" s="380"/>
       <c r="G243" s="160" t="s">
         <v>434</v>
       </c>
@@ -17172,7 +17175,7 @@
       <c r="E244" s="159" t="s">
         <v>428</v>
       </c>
-      <c r="F244" s="381"/>
+      <c r="F244" s="380"/>
       <c r="G244" s="162" t="s">
         <v>435</v>
       </c>
@@ -17182,16 +17185,24 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="F221:F226"/>
-    <mergeCell ref="F227:F232"/>
-    <mergeCell ref="F233:F238"/>
-    <mergeCell ref="F239:F244"/>
-    <mergeCell ref="F185:F190"/>
-    <mergeCell ref="F191:F196"/>
-    <mergeCell ref="F197:F202"/>
-    <mergeCell ref="F203:F208"/>
-    <mergeCell ref="F209:F214"/>
-    <mergeCell ref="F215:F220"/>
+    <mergeCell ref="F35:F40"/>
+    <mergeCell ref="F5:F10"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="F17:F22"/>
+    <mergeCell ref="F23:F28"/>
+    <mergeCell ref="F29:F34"/>
+    <mergeCell ref="F107:F112"/>
+    <mergeCell ref="F41:F46"/>
+    <mergeCell ref="F47:F52"/>
+    <mergeCell ref="F53:F58"/>
+    <mergeCell ref="F59:F64"/>
+    <mergeCell ref="F65:F70"/>
+    <mergeCell ref="F71:F76"/>
+    <mergeCell ref="F77:F82"/>
+    <mergeCell ref="F83:F88"/>
+    <mergeCell ref="F89:F94"/>
+    <mergeCell ref="F95:F100"/>
+    <mergeCell ref="F101:F106"/>
     <mergeCell ref="F179:F184"/>
     <mergeCell ref="F113:F118"/>
     <mergeCell ref="F119:F124"/>
@@ -17204,24 +17215,16 @@
     <mergeCell ref="F161:F166"/>
     <mergeCell ref="F167:F172"/>
     <mergeCell ref="F173:F178"/>
-    <mergeCell ref="F107:F112"/>
-    <mergeCell ref="F41:F46"/>
-    <mergeCell ref="F47:F52"/>
-    <mergeCell ref="F53:F58"/>
-    <mergeCell ref="F59:F64"/>
-    <mergeCell ref="F65:F70"/>
-    <mergeCell ref="F71:F76"/>
-    <mergeCell ref="F77:F82"/>
-    <mergeCell ref="F83:F88"/>
-    <mergeCell ref="F89:F94"/>
-    <mergeCell ref="F95:F100"/>
-    <mergeCell ref="F101:F106"/>
-    <mergeCell ref="F35:F40"/>
-    <mergeCell ref="F5:F10"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="F17:F22"/>
-    <mergeCell ref="F23:F28"/>
-    <mergeCell ref="F29:F34"/>
+    <mergeCell ref="F221:F226"/>
+    <mergeCell ref="F227:F232"/>
+    <mergeCell ref="F233:F238"/>
+    <mergeCell ref="F239:F244"/>
+    <mergeCell ref="F185:F190"/>
+    <mergeCell ref="F191:F196"/>
+    <mergeCell ref="F197:F202"/>
+    <mergeCell ref="F203:F208"/>
+    <mergeCell ref="F209:F214"/>
+    <mergeCell ref="F215:F220"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G12 G14:G16 G35:G41 G44:G58">
     <cfRule type="duplicateValues" dxfId="31" priority="30"/>
